--- a/data/source/team_default.xlsx
+++ b/data/source/team_default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28730"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76929c7f1b9de68b/Documents/Dada/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="84" documentId="11_9F286E40939C4F24CCD8DAA9FE636749AC06DC39" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{22058E5A-49CE-447F-A642-74E3DD1B7089}"/>
+  <xr:revisionPtr revIDLastSave="107" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C133B98-CECD-43F1-BFB5-7BB59224B93B}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -65,85 +65,85 @@
     <t>#392F90</t>
   </si>
   <si>
+    <t>RBR25</t>
+  </si>
+  <si>
     <t>McLaren</t>
   </si>
   <si>
     <t>#ffaa55</t>
   </si>
   <si>
+    <t>MCL25</t>
+  </si>
+  <si>
     <t>Ferrari</t>
   </si>
   <si>
     <t>#E62B2B</t>
   </si>
   <si>
+    <t>FER25</t>
+  </si>
+  <si>
     <t>Mercedes</t>
   </si>
   <si>
     <t>#1BE3B5</t>
   </si>
   <si>
+    <t>MER25</t>
+  </si>
+  <si>
     <t>Haas</t>
   </si>
   <si>
     <t>#bdbdbd</t>
   </si>
   <si>
+    <t>HAA25</t>
+  </si>
+  <si>
     <t>Alpine</t>
   </si>
   <si>
     <t>#ff7ec9</t>
   </si>
   <si>
+    <t>ALP25</t>
+  </si>
+  <si>
     <t>Aston Martin</t>
   </si>
   <si>
     <t>#2d7955</t>
   </si>
   <si>
+    <t>AMR25</t>
+  </si>
+  <si>
     <t>Racing Bulls</t>
   </si>
   <si>
     <t>#3700ff</t>
   </si>
   <si>
+    <t>VRB25</t>
+  </si>
+  <si>
     <t>Williams</t>
   </si>
   <si>
     <t>#46A0EA</t>
   </si>
   <si>
+    <t>WIL25</t>
+  </si>
+  <si>
     <t>Sauber</t>
   </si>
   <si>
     <t>#15ff00</t>
-  </si>
-  <si>
-    <t>RBR25</t>
-  </si>
-  <si>
-    <t>MCL25</t>
-  </si>
-  <si>
-    <t>FER25</t>
-  </si>
-  <si>
-    <t>MER25</t>
-  </si>
-  <si>
-    <t>HAA25</t>
-  </si>
-  <si>
-    <t>ALP25</t>
-  </si>
-  <si>
-    <t>AMR25</t>
-  </si>
-  <si>
-    <t>VRB25</t>
-  </si>
-  <si>
-    <t>WIL25</t>
   </si>
   <si>
     <t>SAU25</t>
@@ -153,7 +153,10 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="2" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
+  </numFmts>
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -164,6 +167,12 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -203,7 +212,9 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -219,6 +230,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -515,7 +530,7 @@
     <col min="1" max="1" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
@@ -552,13 +567,13 @@
         <v>8</v>
       </c>
       <c r="C2" s="1">
-        <v>90</v>
+        <v>93</v>
       </c>
       <c r="D2" s="1">
-        <v>92</v>
+        <v>78</v>
       </c>
       <c r="E2" s="1">
-        <v>88</v>
+        <v>76</v>
       </c>
       <c r="F2" s="1">
         <v>90</v>
@@ -567,7 +582,7 @@
         <v>9</v>
       </c>
       <c r="H2" t="s">
-        <v>28</v>
+        <v>10</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -576,25 +591,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="C3" s="1">
-        <v>93</v>
+        <v>89</v>
       </c>
       <c r="D3" s="1">
-        <v>93</v>
+        <v>83</v>
       </c>
       <c r="E3" s="1">
-        <v>94</v>
+        <v>88</v>
       </c>
       <c r="F3" s="1">
         <v>95</v>
       </c>
       <c r="G3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="H3" t="s">
-        <v>29</v>
+        <v>13</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -603,25 +618,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="C4" s="1">
-        <v>89</v>
+        <v>81</v>
       </c>
       <c r="D4" s="1">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="E4" s="1">
-        <v>88</v>
+        <v>77</v>
       </c>
       <c r="F4" s="1">
         <v>95</v>
       </c>
       <c r="G4" t="s">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="H4" t="s">
-        <v>30</v>
+        <v>16</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -630,13 +645,13 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="C5" s="1">
-        <v>92</v>
+        <v>80</v>
       </c>
       <c r="D5" s="1">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="E5" s="1">
         <v>91</v>
@@ -645,10 +660,10 @@
         <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="H5" t="s">
-        <v>31</v>
+        <v>19</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -657,25 +672,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>16</v>
+        <v>20</v>
       </c>
       <c r="C6" s="1">
-        <v>86</v>
+        <v>94</v>
       </c>
       <c r="D6" s="1">
-        <v>83</v>
+        <v>73</v>
       </c>
       <c r="E6" s="1">
-        <v>82</v>
+        <v>71</v>
       </c>
       <c r="F6" s="1">
         <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>17</v>
+        <v>21</v>
       </c>
       <c r="H6" t="s">
-        <v>32</v>
+        <v>22</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -684,25 +699,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>18</v>
+        <v>23</v>
       </c>
       <c r="C7" s="1">
-        <v>87</v>
+        <v>97</v>
       </c>
       <c r="D7" s="1">
-        <v>89</v>
+        <v>79</v>
       </c>
       <c r="E7" s="1">
-        <v>85</v>
+        <v>70</v>
       </c>
       <c r="F7" s="1">
         <v>90</v>
       </c>
       <c r="G7" t="s">
-        <v>19</v>
+        <v>24</v>
       </c>
       <c r="H7" t="s">
-        <v>33</v>
+        <v>25</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -711,25 +726,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>20</v>
+        <v>26</v>
       </c>
       <c r="C8" s="1">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="D8" s="1">
-        <v>84</v>
+        <v>79</v>
       </c>
       <c r="E8" s="1">
-        <v>85</v>
+        <v>83</v>
       </c>
       <c r="F8" s="1">
         <v>85</v>
       </c>
       <c r="G8" t="s">
-        <v>21</v>
+        <v>27</v>
       </c>
       <c r="H8" t="s">
-        <v>34</v>
+        <v>28</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -738,25 +753,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>22</v>
+        <v>29</v>
       </c>
       <c r="C9" s="1">
-        <v>91</v>
+        <v>96</v>
       </c>
       <c r="D9" s="1">
-        <v>90</v>
+        <v>73</v>
       </c>
       <c r="E9" s="1">
-        <v>89</v>
+        <v>82</v>
       </c>
       <c r="F9" s="1">
         <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>23</v>
+        <v>30</v>
       </c>
       <c r="H9" t="s">
-        <v>35</v>
+        <v>31</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -765,25 +780,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>24</v>
+        <v>32</v>
       </c>
       <c r="C10" s="1">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="D10" s="1">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="E10" s="1">
-        <v>88</v>
+        <v>72</v>
       </c>
       <c r="F10" s="1">
         <v>90</v>
       </c>
       <c r="G10" t="s">
-        <v>25</v>
+        <v>33</v>
       </c>
       <c r="H10" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -792,22 +807,22 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
-        <v>26</v>
+        <v>35</v>
       </c>
       <c r="C11" s="1">
-        <v>83</v>
+        <v>93</v>
       </c>
       <c r="D11" s="1">
-        <v>83</v>
+        <v>79</v>
       </c>
       <c r="E11" s="1">
-        <v>83</v>
+        <v>75</v>
       </c>
       <c r="F11" s="1">
         <v>90</v>
       </c>
       <c r="G11" t="s">
-        <v>27</v>
+        <v>36</v>
       </c>
       <c r="H11" t="s">
         <v>37</v>

--- a/data/source/team_default.xlsx
+++ b/data/source/team_default.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76929c7f1b9de68b/Documents/Dada/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="107" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2C133B98-CECD-43F1-BFB5-7BB59224B93B}"/>
+  <xr:revisionPtr revIDLastSave="186" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF8E2FF-22A2-4FB4-8DB0-27B46B87944B}"/>
   <bookViews>
     <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="38" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
   <si>
     <t>team_id</t>
   </si>
@@ -65,88 +65,97 @@
     <t>#392F90</t>
   </si>
   <si>
-    <t>RBR25</t>
-  </si>
-  <si>
     <t>McLaren</t>
   </si>
   <si>
     <t>#ffaa55</t>
   </si>
   <si>
-    <t>MCL25</t>
-  </si>
-  <si>
     <t>Ferrari</t>
   </si>
   <si>
     <t>#E62B2B</t>
   </si>
   <si>
-    <t>FER25</t>
-  </si>
-  <si>
     <t>Mercedes</t>
   </si>
   <si>
     <t>#1BE3B5</t>
   </si>
   <si>
-    <t>MER25</t>
-  </si>
-  <si>
     <t>Haas</t>
   </si>
   <si>
     <t>#bdbdbd</t>
   </si>
   <si>
-    <t>HAA25</t>
-  </si>
-  <si>
     <t>Alpine</t>
   </si>
   <si>
     <t>#ff7ec9</t>
   </si>
   <si>
-    <t>ALP25</t>
-  </si>
-  <si>
     <t>Aston Martin</t>
   </si>
   <si>
     <t>#2d7955</t>
   </si>
   <si>
-    <t>AMR25</t>
-  </si>
-  <si>
     <t>Racing Bulls</t>
   </si>
   <si>
     <t>#3700ff</t>
   </si>
   <si>
-    <t>VRB25</t>
-  </si>
-  <si>
     <t>Williams</t>
   </si>
   <si>
     <t>#46A0EA</t>
   </si>
   <si>
-    <t>WIL25</t>
-  </si>
-  <si>
-    <t>Sauber</t>
-  </si>
-  <si>
-    <t>#15ff00</t>
-  </si>
-  <si>
-    <t>SAU25</t>
+    <t>Audi</t>
+  </si>
+  <si>
+    <t>Cadillac</t>
+  </si>
+  <si>
+    <t>#fff</t>
+  </si>
+  <si>
+    <t>#f00</t>
+  </si>
+  <si>
+    <t>RBR26</t>
+  </si>
+  <si>
+    <t>MCL26</t>
+  </si>
+  <si>
+    <t>FER26</t>
+  </si>
+  <si>
+    <t>MER26</t>
+  </si>
+  <si>
+    <t>HAA26</t>
+  </si>
+  <si>
+    <t>ALP26</t>
+  </si>
+  <si>
+    <t>AST26</t>
+  </si>
+  <si>
+    <t>VRB26</t>
+  </si>
+  <si>
+    <t>WIL26</t>
+  </si>
+  <si>
+    <t>AUD26</t>
+  </si>
+  <si>
+    <t>CAD26</t>
   </si>
 </sst>
 </file>
@@ -524,7 +533,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J11"/>
+  <dimension ref="A1:J12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
@@ -564,25 +573,25 @@
         <v>1</v>
       </c>
       <c r="B2" t="s">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="C2" s="1">
-        <v>93</v>
+        <v>88.67078847953853</v>
       </c>
       <c r="D2" s="1">
-        <v>78</v>
+        <v>94.633197539354015</v>
       </c>
       <c r="E2" s="1">
-        <v>76</v>
+        <v>89.600966266349815</v>
       </c>
       <c r="F2" s="1">
-        <v>90</v>
+        <v>75</v>
       </c>
       <c r="G2" t="s">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="H2" t="s">
-        <v>10</v>
+        <v>31</v>
       </c>
       <c r="J2" s="3"/>
     </row>
@@ -591,25 +600,25 @@
         <v>2</v>
       </c>
       <c r="B3" t="s">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="C3" s="1">
-        <v>89</v>
+        <v>94.739918855340974</v>
       </c>
       <c r="D3" s="1">
-        <v>83</v>
+        <v>99</v>
       </c>
       <c r="E3" s="1">
-        <v>88</v>
+        <v>98.591876315375643</v>
       </c>
       <c r="F3" s="1">
         <v>95</v>
       </c>
       <c r="G3" t="s">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="H3" t="s">
-        <v>13</v>
+        <v>33</v>
       </c>
       <c r="J3" s="3"/>
     </row>
@@ -618,25 +627,25 @@
         <v>3</v>
       </c>
       <c r="B4" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>81</v>
+        <v>91.655682319362256</v>
       </c>
       <c r="D4" s="1">
-        <v>92</v>
+        <v>84.507590715001001</v>
       </c>
       <c r="E4" s="1">
-        <v>77</v>
+        <v>86.170334395677557</v>
       </c>
       <c r="F4" s="1">
-        <v>95</v>
+        <v>90</v>
       </c>
       <c r="G4" t="s">
-        <v>15</v>
+        <v>9</v>
       </c>
       <c r="H4" t="s">
-        <v>16</v>
+        <v>30</v>
       </c>
       <c r="J4" s="3"/>
     </row>
@@ -645,25 +654,25 @@
         <v>4</v>
       </c>
       <c r="B5" t="s">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="C5" s="1">
-        <v>80</v>
+        <v>99</v>
       </c>
       <c r="D5" s="1">
-        <v>89</v>
+        <v>88.530214990016916</v>
       </c>
       <c r="E5" s="1">
-        <v>91</v>
+        <v>90.280097722659875</v>
       </c>
       <c r="F5" s="1">
         <v>95</v>
       </c>
       <c r="G5" t="s">
-        <v>18</v>
+        <v>13</v>
       </c>
       <c r="H5" t="s">
-        <v>19</v>
+        <v>32</v>
       </c>
       <c r="J5" s="3"/>
     </row>
@@ -672,25 +681,25 @@
         <v>5</v>
       </c>
       <c r="B6" t="s">
-        <v>20</v>
+        <v>24</v>
       </c>
       <c r="C6" s="1">
-        <v>94</v>
+        <v>78.063941156175247</v>
       </c>
       <c r="D6" s="1">
-        <v>73</v>
+        <v>79.480268085662431</v>
       </c>
       <c r="E6" s="1">
-        <v>71</v>
+        <v>81.945818186527617</v>
       </c>
       <c r="F6" s="1">
         <v>95</v>
       </c>
       <c r="G6" t="s">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="H6" t="s">
-        <v>22</v>
+        <v>38</v>
       </c>
       <c r="J6" s="3"/>
     </row>
@@ -699,25 +708,25 @@
         <v>6</v>
       </c>
       <c r="B7" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="C7" s="1">
-        <v>97</v>
+        <v>93.887805067783248</v>
       </c>
       <c r="D7" s="1">
-        <v>79</v>
+        <v>83.346702822761955</v>
       </c>
       <c r="E7" s="1">
-        <v>70</v>
+        <v>86.270574228061548</v>
       </c>
       <c r="F7" s="1">
         <v>90</v>
       </c>
       <c r="G7" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="H7" t="s">
-        <v>25</v>
+        <v>37</v>
       </c>
       <c r="J7" s="3"/>
     </row>
@@ -726,25 +735,25 @@
         <v>7</v>
       </c>
       <c r="B8" t="s">
-        <v>26</v>
+        <v>20</v>
       </c>
       <c r="C8" s="1">
-        <v>85</v>
+        <v>66.41003355675393</v>
       </c>
       <c r="D8" s="1">
-        <v>79</v>
+        <v>69.113134025949194</v>
       </c>
       <c r="E8" s="1">
-        <v>83</v>
+        <v>73.31094610384676</v>
       </c>
       <c r="F8" s="1">
-        <v>85</v>
+        <v>60</v>
       </c>
       <c r="G8" t="s">
-        <v>27</v>
+        <v>21</v>
       </c>
       <c r="H8" t="s">
-        <v>28</v>
+        <v>36</v>
       </c>
       <c r="J8" s="3"/>
     </row>
@@ -753,25 +762,25 @@
         <v>8</v>
       </c>
       <c r="B9" t="s">
-        <v>29</v>
+        <v>16</v>
       </c>
       <c r="C9" s="1">
-        <v>96</v>
+        <v>81.430903927630041</v>
       </c>
       <c r="D9" s="1">
-        <v>73</v>
+        <v>79.649776615714885</v>
       </c>
       <c r="E9" s="1">
-        <v>82</v>
+        <v>96.198598036355364</v>
       </c>
       <c r="F9" s="1">
         <v>90</v>
       </c>
       <c r="G9" t="s">
-        <v>30</v>
+        <v>17</v>
       </c>
       <c r="H9" t="s">
-        <v>31</v>
+        <v>34</v>
       </c>
       <c r="J9" s="3"/>
     </row>
@@ -780,25 +789,25 @@
         <v>9</v>
       </c>
       <c r="B10" t="s">
-        <v>32</v>
+        <v>26</v>
       </c>
       <c r="C10" s="1">
-        <v>86</v>
+        <v>96.071951453014037</v>
       </c>
       <c r="D10" s="1">
-        <v>91</v>
+        <v>87.227089968891377</v>
       </c>
       <c r="E10" s="1">
-        <v>72</v>
+        <v>80.743632934185015</v>
       </c>
       <c r="F10" s="1">
-        <v>90</v>
+        <v>95</v>
       </c>
       <c r="G10" t="s">
-        <v>33</v>
+        <v>29</v>
       </c>
       <c r="H10" t="s">
-        <v>34</v>
+        <v>39</v>
       </c>
       <c r="J10" s="3"/>
     </row>
@@ -807,29 +816,58 @@
         <v>10</v>
       </c>
       <c r="B11" t="s">
+        <v>18</v>
+      </c>
+      <c r="C11" s="1">
+        <v>88.346311395322431</v>
+      </c>
+      <c r="D11" s="1">
+        <v>89.343868706405971</v>
+      </c>
+      <c r="E11" s="1">
+        <v>84.603003841245553</v>
+      </c>
+      <c r="F11" s="1">
+        <v>95</v>
+      </c>
+      <c r="G11" t="s">
+        <v>19</v>
+      </c>
+      <c r="H11" t="s">
         <v>35</v>
       </c>
-      <c r="C11" s="1">
-        <v>93</v>
-      </c>
-      <c r="D11" s="1">
-        <v>79</v>
-      </c>
-      <c r="E11" s="1">
-        <v>75</v>
-      </c>
-      <c r="F11" s="1">
-        <v>90</v>
-      </c>
-      <c r="G11" t="s">
-        <v>36</v>
-      </c>
-      <c r="H11" t="s">
-        <v>37</v>
-      </c>
       <c r="J11" s="3"/>
     </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+      <c r="A12" s="2">
+        <v>11</v>
+      </c>
+      <c r="B12" t="s">
+        <v>27</v>
+      </c>
+      <c r="C12" s="2">
+        <v>67.425549294530711</v>
+      </c>
+      <c r="D12" s="2">
+        <v>66.433137506316513</v>
+      </c>
+      <c r="E12" s="2">
+        <v>67.453950273469957</v>
+      </c>
+      <c r="F12" s="2">
+        <v>95</v>
+      </c>
+      <c r="G12" t="s">
+        <v>28</v>
+      </c>
+      <c r="H12" t="s">
+        <v>40</v>
+      </c>
+    </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="A2:H12">
+    <sortCondition ref="A4:A12"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/data/source/team_default.xlsx
+++ b/data/source/team_default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76929c7f1b9de68b/Documents/Dada/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="186" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3CF8E2FF-22A2-4FB4-8DB0-27B46B87944B}"/>
+  <xr:revisionPtr revIDLastSave="253" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1981270A-02A2-4F70-AD09-2C42F8B721FB}"/>
   <bookViews>
-    <workbookView xWindow="28695" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -162,10 +162,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="#,##0.000"/>
-  </numFmts>
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -176,12 +173,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
     </font>
@@ -213,15 +204,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
   </cellXfs>
@@ -239,10 +227,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -533,16 +517,16 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:J12"/>
+  <dimension ref="A1:H12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="10" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -568,7 +552,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -576,16 +560,16 @@
         <v>10</v>
       </c>
       <c r="C2" s="1">
-        <v>88.67078847953853</v>
+        <v>93.186569091493737</v>
       </c>
       <c r="D2" s="1">
-        <v>94.633197539354015</v>
+        <v>92.998775716054823</v>
       </c>
       <c r="E2" s="1">
-        <v>89.600966266349815</v>
+        <v>91.700379317989444</v>
       </c>
       <c r="F2" s="1">
-        <v>75</v>
+        <v>73</v>
       </c>
       <c r="G2" t="s">
         <v>11</v>
@@ -593,9 +577,8 @@
       <c r="H2" t="s">
         <v>31</v>
       </c>
-      <c r="J2" s="3"/>
-    </row>
-    <row r="3" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -603,16 +586,16 @@
         <v>14</v>
       </c>
       <c r="C3" s="1">
-        <v>94.739918855340974</v>
+        <v>98.591742200289744</v>
       </c>
       <c r="D3" s="1">
         <v>99</v>
       </c>
       <c r="E3" s="1">
-        <v>98.591876315375643</v>
+        <v>97.816415805586018</v>
       </c>
       <c r="F3" s="1">
-        <v>95</v>
+        <v>86</v>
       </c>
       <c r="G3" t="s">
         <v>15</v>
@@ -620,9 +603,8 @@
       <c r="H3" t="s">
         <v>33</v>
       </c>
-      <c r="J3" s="3"/>
-    </row>
-    <row r="4" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -630,16 +612,16 @@
         <v>8</v>
       </c>
       <c r="C4" s="1">
-        <v>91.655682319362256</v>
+        <v>99</v>
       </c>
       <c r="D4" s="1">
-        <v>84.507590715001001</v>
+        <v>80.816592273637511</v>
       </c>
       <c r="E4" s="1">
-        <v>86.170334395677557</v>
+        <v>94.920069445983714</v>
       </c>
       <c r="F4" s="1">
-        <v>90</v>
+        <v>82</v>
       </c>
       <c r="G4" t="s">
         <v>9</v>
@@ -647,9 +629,8 @@
       <c r="H4" t="s">
         <v>30</v>
       </c>
-      <c r="J4" s="3"/>
-    </row>
-    <row r="5" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -657,16 +638,16 @@
         <v>12</v>
       </c>
       <c r="C5" s="1">
-        <v>99</v>
+        <v>95.12227356213829</v>
       </c>
       <c r="D5" s="1">
-        <v>88.530214990016916</v>
+        <v>93.071176337169973</v>
       </c>
       <c r="E5" s="1">
-        <v>90.280097722659875</v>
+        <v>95.474026934885984</v>
       </c>
       <c r="F5" s="1">
-        <v>95</v>
+        <v>91</v>
       </c>
       <c r="G5" t="s">
         <v>13</v>
@@ -674,9 +655,8 @@
       <c r="H5" t="s">
         <v>32</v>
       </c>
-      <c r="J5" s="3"/>
-    </row>
-    <row r="6" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -684,16 +664,16 @@
         <v>24</v>
       </c>
       <c r="C6" s="1">
-        <v>78.063941156175247</v>
+        <v>87.605962450352536</v>
       </c>
       <c r="D6" s="1">
-        <v>79.480268085662431</v>
+        <v>68.176662298611603</v>
       </c>
       <c r="E6" s="1">
-        <v>81.945818186527617</v>
+        <v>79.622325668483697</v>
       </c>
       <c r="F6" s="1">
-        <v>95</v>
+        <v>82</v>
       </c>
       <c r="G6" t="s">
         <v>25</v>
@@ -701,9 +681,8 @@
       <c r="H6" t="s">
         <v>38</v>
       </c>
-      <c r="J6" s="3"/>
-    </row>
-    <row r="7" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -711,16 +690,16 @@
         <v>22</v>
       </c>
       <c r="C7" s="1">
-        <v>93.887805067783248</v>
+        <v>93.16650754286087</v>
       </c>
       <c r="D7" s="1">
-        <v>83.346702822761955</v>
+        <v>95.606254937916944</v>
       </c>
       <c r="E7" s="1">
-        <v>86.270574228061548</v>
+        <v>83.876628989201791</v>
       </c>
       <c r="F7" s="1">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G7" t="s">
         <v>23</v>
@@ -728,9 +707,8 @@
       <c r="H7" t="s">
         <v>37</v>
       </c>
-      <c r="J7" s="3"/>
-    </row>
-    <row r="8" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="8" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -738,13 +716,13 @@
         <v>20</v>
       </c>
       <c r="C8" s="1">
-        <v>66.41003355675393</v>
+        <v>66.222479398391002</v>
       </c>
       <c r="D8" s="1">
-        <v>69.113134025949194</v>
+        <v>66</v>
       </c>
       <c r="E8" s="1">
-        <v>73.31094610384676</v>
+        <v>70.833113647780834</v>
       </c>
       <c r="F8" s="1">
         <v>60</v>
@@ -755,9 +733,8 @@
       <c r="H8" t="s">
         <v>36</v>
       </c>
-      <c r="J8" s="3"/>
-    </row>
-    <row r="9" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -765,16 +742,16 @@
         <v>16</v>
       </c>
       <c r="C9" s="1">
-        <v>81.430903927630041</v>
+        <v>93.874372465592231</v>
       </c>
       <c r="D9" s="1">
-        <v>79.649776615714885</v>
+        <v>77.437510971247832</v>
       </c>
       <c r="E9" s="1">
-        <v>96.198598036355364</v>
+        <v>70.41998504191838</v>
       </c>
       <c r="F9" s="1">
-        <v>90</v>
+        <v>86</v>
       </c>
       <c r="G9" t="s">
         <v>17</v>
@@ -782,9 +759,8 @@
       <c r="H9" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="3"/>
-    </row>
-    <row r="10" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -792,16 +768,16 @@
         <v>26</v>
       </c>
       <c r="C10" s="1">
-        <v>96.071951453014037</v>
+        <v>91.03773149834042</v>
       </c>
       <c r="D10" s="1">
-        <v>87.227089968891377</v>
+        <v>91.556053702162828</v>
       </c>
       <c r="E10" s="1">
-        <v>80.743632934185015</v>
+        <v>85.329606437671899</v>
       </c>
       <c r="F10" s="1">
-        <v>95</v>
+        <v>73</v>
       </c>
       <c r="G10" t="s">
         <v>29</v>
@@ -809,9 +785,8 @@
       <c r="H10" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="3"/>
-    </row>
-    <row r="11" spans="1:10" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    </row>
+    <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -819,13 +794,13 @@
         <v>18</v>
       </c>
       <c r="C11" s="1">
-        <v>88.346311395322431</v>
+        <v>92.837995250898345</v>
       </c>
       <c r="D11" s="1">
-        <v>89.343868706405971</v>
+        <v>78.893694734702422</v>
       </c>
       <c r="E11" s="1">
-        <v>84.603003841245553</v>
+        <v>88.570765252801351</v>
       </c>
       <c r="F11" s="1">
         <v>95</v>
@@ -836,9 +811,8 @@
       <c r="H11" t="s">
         <v>35</v>
       </c>
-      <c r="J11" s="3"/>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.25">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -846,16 +820,16 @@
         <v>27</v>
       </c>
       <c r="C12" s="2">
-        <v>67.425549294530711</v>
+        <v>76.677833541820121</v>
       </c>
       <c r="D12" s="2">
-        <v>66.433137506316513</v>
+        <v>69.280703871440195</v>
       </c>
       <c r="E12" s="2">
-        <v>67.453950273469957</v>
+        <v>66</v>
       </c>
       <c r="F12" s="2">
-        <v>95</v>
+        <v>56</v>
       </c>
       <c r="G12" t="s">
         <v>28</v>

--- a/data/source/team_default.xlsx
+++ b/data/source/team_default.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30228"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/76929c7f1b9de68b/Documents/Dada/data/source/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="253" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{1981270A-02A2-4F70-AD09-2C42F8B721FB}"/>
+  <xr:revisionPtr revIDLastSave="267" documentId="11_8F20ED55937C482908FC15CAFFAB6FCF8E869301" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{8D699408-BA55-4608-91CE-19256F248B0E}"/>
   <bookViews>
-    <workbookView xWindow="-105" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="14295" yWindow="0" windowWidth="14610" windowHeight="15585" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Feuil1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="41" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="48">
   <si>
     <t>team_id</t>
   </si>
@@ -156,6 +156,27 @@
   </si>
   <si>
     <t>CAD26</t>
+  </si>
+  <si>
+    <t>flag</t>
+  </si>
+  <si>
+    <t>uk.png</t>
+  </si>
+  <si>
+    <t>germany.png</t>
+  </si>
+  <si>
+    <t>austria.png</t>
+  </si>
+  <si>
+    <t>italy.png</t>
+  </si>
+  <si>
+    <t>usa.png</t>
+  </si>
+  <si>
+    <t>france.png</t>
   </si>
 </sst>
 </file>
@@ -204,7 +225,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right"/>
@@ -212,6 +233,7 @@
     <xf numFmtId="3" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
+    <xf numFmtId="3" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -517,16 +539,17 @@
   <sheetPr>
     <outlinePr summaryBelow="0"/>
   </sheetPr>
-  <dimension ref="A1:H12"/>
+  <dimension ref="A1:I12"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="13.5703125" style="2" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.140625" bestFit="1" customWidth="1"/>
     <col min="3" max="6" width="5.28515625" style="2" bestFit="1" customWidth="1"/>
     <col min="7" max="8" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="12.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -551,8 +574,11 @@
       <c r="H1" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="2" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I1" s="3" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="1">
         <v>1</v>
       </c>
@@ -577,8 +603,11 @@
       <c r="H2" t="s">
         <v>31</v>
       </c>
-    </row>
-    <row r="3" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I2" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="3" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="1">
         <v>2</v>
       </c>
@@ -603,8 +632,11 @@
       <c r="H3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="4" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I3" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="4" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A4" s="1">
         <v>3</v>
       </c>
@@ -629,8 +661,11 @@
       <c r="H4" t="s">
         <v>30</v>
       </c>
-    </row>
-    <row r="5" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I4" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="5" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A5" s="1">
         <v>4</v>
       </c>
@@ -655,8 +690,11 @@
       <c r="H5" t="s">
         <v>32</v>
       </c>
-    </row>
-    <row r="6" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="6" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A6" s="1">
         <v>5</v>
       </c>
@@ -681,8 +719,11 @@
       <c r="H6" t="s">
         <v>38</v>
       </c>
-    </row>
-    <row r="7" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I6" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="7" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A7" s="1">
         <v>6</v>
       </c>
@@ -707,8 +748,11 @@
       <c r="H7" t="s">
         <v>37</v>
       </c>
-    </row>
-    <row r="8" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I7" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="8" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A8" s="1">
         <v>7</v>
       </c>
@@ -733,8 +777,11 @@
       <c r="H8" t="s">
         <v>36</v>
       </c>
-    </row>
-    <row r="9" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I8" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="9" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A9" s="1">
         <v>8</v>
       </c>
@@ -759,8 +806,11 @@
       <c r="H9" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="10" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I9" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="10" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="1">
         <v>9</v>
       </c>
@@ -785,8 +835,11 @@
       <c r="H10" t="s">
         <v>39</v>
       </c>
-    </row>
-    <row r="11" spans="1:8" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="I10" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="11" spans="1:9" ht="19.5" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A11" s="1">
         <v>10</v>
       </c>
@@ -811,8 +864,11 @@
       <c r="H11" t="s">
         <v>35</v>
       </c>
-    </row>
-    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
+      <c r="I11" t="s">
+        <v>47</v>
+      </c>
+    </row>
+    <row r="12" spans="1:9" x14ac:dyDescent="0.25">
       <c r="A12" s="2">
         <v>11</v>
       </c>
@@ -836,6 +892,9 @@
       </c>
       <c r="H12" t="s">
         <v>40</v>
+      </c>
+      <c r="I12" t="s">
+        <v>46</v>
       </c>
     </row>
   </sheetData>
